--- a/artfynd/A 30187-2023 artfynd.xlsx
+++ b/artfynd/A 30187-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30187-2023 artfynd.xlsx
+++ b/artfynd/A 30187-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106640087</v>
+        <v>106640072</v>
       </c>
       <c r="B2" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,21 +708,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brattåker, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>756850</v>
+        <v>756831</v>
       </c>
       <c r="R2" t="n">
-        <v>7108416</v>
+        <v>7108610</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -770,11 +760,6 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -816,37 +801,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106640090</v>
+        <v>106640071</v>
       </c>
       <c r="B3" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -854,21 +834,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brattåker, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>756856</v>
+        <v>756852</v>
       </c>
       <c r="R3" t="n">
-        <v>7108568</v>
+        <v>7108565</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -911,11 +886,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -957,19 +927,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106640119</v>
+        <v>106640116</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1001,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>756840.9304841018</v>
+        <v>756981</v>
       </c>
       <c r="R4" t="n">
-        <v>7108515.159261605</v>
+        <v>7108385</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1088,37 +1053,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106640092</v>
+        <v>106640117</v>
       </c>
       <c r="B5" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1126,21 +1086,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Brattåker, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>756828</v>
+        <v>756822</v>
       </c>
       <c r="R5" t="n">
-        <v>7108639</v>
+        <v>7108447</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1183,11 +1138,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>äldre använt bohål</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1229,37 +1179,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106640098</v>
+        <v>106640118</v>
       </c>
       <c r="B6" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1273,10 +1218,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>756821.4216897794</v>
+        <v>756829</v>
       </c>
       <c r="R6" t="n">
-        <v>7108447.02294857</v>
+        <v>7108499</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1332,17 +1277,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1360,37 +1305,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>106640071</v>
+        <v>106640119</v>
       </c>
       <c r="B7" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1404,10 +1344,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>756852.2113101224</v>
+        <v>756841</v>
       </c>
       <c r="R7" t="n">
-        <v>7108565.43289487</v>
+        <v>7108515</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1491,37 +1431,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>106640100</v>
+        <v>106640120</v>
       </c>
       <c r="B8" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1529,21 +1464,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Brattåker, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>756865</v>
+        <v>756832</v>
       </c>
       <c r="R8" t="n">
-        <v>7108396</v>
+        <v>7108611</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1586,11 +1516,6 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>3 träd, födosök efter hästmyror</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1632,37 +1557,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>106640091</v>
+        <v>106640121</v>
       </c>
       <c r="B9" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1670,21 +1590,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brattåker, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>756845</v>
+        <v>756849</v>
       </c>
       <c r="R9" t="n">
-        <v>7108570</v>
+        <v>7108663</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1727,11 +1642,6 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1773,37 +1683,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>106640094</v>
+        <v>106640122</v>
       </c>
       <c r="B10" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1811,21 +1716,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brattåker, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>756832</v>
+        <v>756859</v>
       </c>
       <c r="R10" t="n">
-        <v>7108417</v>
+        <v>7108751</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1868,11 +1768,6 @@
       <c r="AB10" t="inlineStr">
         <is>
           <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1914,37 +1809,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>106640120</v>
+        <v>106640098</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1958,10 +1848,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>756832.5310682817</v>
+        <v>756822</v>
       </c>
       <c r="R11" t="n">
-        <v>7108611.382870955</v>
+        <v>7108447</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2017,17 +1907,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2045,32 +1935,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>106640103</v>
+        <v>106640100</v>
       </c>
       <c r="B12" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2094,10 +1979,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>756824</v>
+        <v>756865</v>
       </c>
       <c r="R12" t="n">
-        <v>7108450</v>
+        <v>7108396</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2144,7 +2029,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>3 träd, födosök efter hästmyror</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2158,17 +2043,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2186,37 +2071,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>106640126</v>
+        <v>106640074</v>
       </c>
       <c r="B13" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2224,16 +2104,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brattåker, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>756860.3080574364</v>
+        <v>756833</v>
       </c>
       <c r="R13" t="n">
-        <v>7108403.539930978</v>
+        <v>7108511</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2276,6 +2161,11 @@
       <c r="AB13" t="inlineStr">
         <is>
           <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2317,15 +2207,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>106640072</v>
+        <v>106640075</v>
       </c>
       <c r="B14" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2333,21 +2218,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2355,16 +2240,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brattåker, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>756830.4129208403</v>
+        <v>756840</v>
       </c>
       <c r="R14" t="n">
-        <v>7108610.32662499</v>
+        <v>7108517</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2407,6 +2297,11 @@
       <c r="AB14" t="inlineStr">
         <is>
           <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2448,15 +2343,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>106640086</v>
+        <v>106640078</v>
       </c>
       <c r="B15" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2497,10 +2387,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>756859</v>
+        <v>756832</v>
       </c>
       <c r="R15" t="n">
-        <v>7108415</v>
+        <v>7108639</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2589,15 +2479,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>106640078</v>
+        <v>106640086</v>
       </c>
       <c r="B16" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2638,10 +2523,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>756832</v>
+        <v>756859</v>
       </c>
       <c r="R16" t="n">
-        <v>7108639</v>
+        <v>7108415</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2730,15 +2615,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>106640074</v>
+        <v>106640087</v>
       </c>
       <c r="B17" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2770,7 +2650,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2779,10 +2659,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>756833</v>
+        <v>756850</v>
       </c>
       <c r="R17" t="n">
-        <v>7108511</v>
+        <v>7108416</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2829,7 +2709,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2871,15 +2751,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>106640117</v>
+        <v>106640088</v>
       </c>
       <c r="B18" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2887,21 +2762,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2909,16 +2784,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Brattåker, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>756821.4216897794</v>
+        <v>756842</v>
       </c>
       <c r="R18" t="n">
-        <v>7108447.02294857</v>
+        <v>7108416</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2961,6 +2841,11 @@
       <c r="AB18" t="inlineStr">
         <is>
           <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3002,15 +2887,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>106640088</v>
+        <v>106640089</v>
       </c>
       <c r="B19" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3042,7 +2922,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3051,10 +2931,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>756842</v>
+        <v>756834</v>
       </c>
       <c r="R19" t="n">
-        <v>7108416</v>
+        <v>7108457</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3143,15 +3023,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>106640122</v>
+        <v>106640090</v>
       </c>
       <c r="B20" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3159,21 +3034,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3181,16 +3056,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brattåker, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>756858.8799244283</v>
+        <v>756856</v>
       </c>
       <c r="R20" t="n">
-        <v>7108751.445495646</v>
+        <v>7108568</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3233,6 +3113,11 @@
       <c r="AB20" t="inlineStr">
         <is>
           <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3274,15 +3159,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>106640075</v>
+        <v>106640091</v>
       </c>
       <c r="B21" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3323,10 +3203,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>756840</v>
+        <v>756845</v>
       </c>
       <c r="R21" t="n">
-        <v>7108517</v>
+        <v>7108570</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3373,7 +3253,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3415,15 +3295,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>106640118</v>
+        <v>106640092</v>
       </c>
       <c r="B22" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3431,21 +3306,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3453,16 +3328,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Brattåker, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>756829.0172841777</v>
+        <v>756828</v>
       </c>
       <c r="R22" t="n">
-        <v>7108499.195446693</v>
+        <v>7108639</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3505,6 +3385,11 @@
       <c r="AB22" t="inlineStr">
         <is>
           <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>äldre använt bohål</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3546,15 +3431,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>106640121</v>
+        <v>106640093</v>
       </c>
       <c r="B23" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3562,21 +3442,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3584,16 +3464,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Brattåker, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>756848.9601176826</v>
+        <v>756878</v>
       </c>
       <c r="R23" t="n">
-        <v>7108663.4023812</v>
+        <v>7108403</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3636,6 +3521,11 @@
       <c r="AB23" t="inlineStr">
         <is>
           <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>2 påbörjade bohål</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3677,15 +3567,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>106640093</v>
+        <v>106640094</v>
       </c>
       <c r="B24" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3717,7 +3602,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3726,10 +3611,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>756878</v>
+        <v>756832</v>
       </c>
       <c r="R24" t="n">
-        <v>7108403</v>
+        <v>7108417</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3776,7 +3661,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2 påbörjade bohål</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3818,15 +3703,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>106640104</v>
+        <v>106640103</v>
       </c>
       <c r="B25" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3867,10 +3747,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>756831</v>
+        <v>756824</v>
       </c>
       <c r="R25" t="n">
-        <v>7108472</v>
+        <v>7108450</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3931,17 +3811,17 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3959,15 +3839,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>106640089</v>
+        <v>106640104</v>
       </c>
       <c r="B26" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3999,7 +3874,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -4008,10 +3883,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>756834</v>
+        <v>756831</v>
       </c>
       <c r="R26" t="n">
-        <v>7108457</v>
+        <v>7108472</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4058,7 +3933,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4097,6 +3972,132 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>106640126</v>
+      </c>
+      <c r="B27" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Brattåker, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>756860</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7108404</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-02-11</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-02-11</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jon Andersson, Linnea Helmersson, Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30187-2023 artfynd.xlsx
+++ b/artfynd/A 30187-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106640072</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106640071</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1050,6 +1065,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106640116</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1176,6 +1196,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106640117</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1302,6 +1327,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106640118</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1428,6 +1458,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106640119</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1554,6 +1589,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106640120</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1680,6 +1720,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106640121</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1806,6 +1851,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106640122</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1932,6 +1982,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106640098</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2068,6 +2123,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106640100</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2204,6 +2264,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106640074</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2340,6 +2405,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106640075</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2476,6 +2546,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106640078</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2612,6 +2687,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106640086</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2748,6 +2828,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106640087</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2884,6 +2969,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106640088</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3020,6 +3110,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106640089</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3156,6 +3251,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106640090</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3292,6 +3392,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106640091</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3428,6 +3533,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106640092</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3564,6 +3674,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106640093</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3700,6 +3815,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106640094</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3836,6 +3956,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106640103</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3972,6 +4097,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106640104</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4098,8 +4228,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106640126</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>